--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>117559016</v>
       </c>
       <c r="B3" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,140 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123712434</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58352</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>lillbäcken, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596760</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6547891</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Zet Bjällquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Zet Bjällquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>123712434</v>
       </c>
       <c r="B4" t="n">
-        <v>58352</v>
+        <v>58358</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>123712434</v>
       </c>
       <c r="B4" t="n">
-        <v>58358</v>
+        <v>58361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>123712434</v>
       </c>
       <c r="B4" t="n">
-        <v>58361</v>
+        <v>58362</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,6 +1036,113 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126277468</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105931</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hagalid O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596966</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6547915</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>126277468</v>
       </c>
       <c r="B5" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>126277468</v>
       </c>
       <c r="B5" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>126277468</v>
       </c>
       <c r="B5" t="n">
-        <v>105947</v>
+        <v>105956</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -907,12 +907,7 @@
         <v>123712434</v>
       </c>
       <c r="B4" t="n">
-        <v>58384</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>123712434</v>
       </c>
       <c r="B4" t="n">
-        <v>58765</v>
+        <v>58766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58779285</v>
+        <v>123712434</v>
       </c>
       <c r="B2" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219716</v>
+        <v>100141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väsby, 400 m NNV om, Srm</t>
+          <t>lillbäcken, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596418.4383850467</v>
+        <v>596760</v>
       </c>
       <c r="R2" t="n">
-        <v>6547744.097294381</v>
+        <v>6547891</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1991-08-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1991-08-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,66 +785,61 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gräsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Zet Bjällquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Zet Bjällquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117559016</v>
+        <v>120412898</v>
       </c>
       <c r="B3" t="n">
-        <v>105486</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>206046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -866,12 +877,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,14 +891,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,69 +909,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123712434</v>
+        <v>58779285</v>
       </c>
       <c r="B4" t="n">
-        <v>58788</v>
+        <v>111399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100141</v>
+        <v>219716</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>lillbäcken, Srm</t>
+          <t>Väsby, 400 m NNV om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596760</v>
+        <v>596418</v>
       </c>
       <c r="R4" t="n">
-        <v>6547891</v>
+        <v>6547744</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,22 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>22:30</t>
+          <t>1991-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>1991-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,46 +988,50 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>gräsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Zet Bjällquist</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Zet Bjällquist</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126277468</v>
+        <v>7180976</v>
       </c>
       <c r="B5" t="n">
-        <v>105956</v>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,20 +1040,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagalid O om, Srm</t>
+          <t>Väsby, järnvägen NV om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596966</v>
+        <v>596428</v>
       </c>
       <c r="R5" t="n">
-        <v>6547915</v>
+        <v>6547936</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,17 +1071,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Helgesta</t>
+          <t>Flen</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>1991-08-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>1991-08-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,27 +1090,240 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>järnvägsbank</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117559016</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hagalid 150m VSV, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596773</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6547893</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126277468</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hagalid O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596966</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6547915</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4551-2023 artfynd.xlsx
+++ b/artfynd/A 4551-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712434</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120412898</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58779285</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7180976</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117559016</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,8 +1354,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126277468</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>